--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753713755_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753713755_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008402251151435237</v>
       </c>
       <c r="C2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>9814984</v>
+        <v>4821812</v>
       </c>
       <c r="L2" t="n">
-        <v>6200368</v>
+        <v>2962933</v>
       </c>
       <c r="M2" t="n">
-        <v>1665521</v>
+        <v>779586</v>
       </c>
       <c r="N2" t="n">
-        <v>105516</v>
+        <v>44508</v>
       </c>
       <c r="O2" t="n">
-        <v>963183</v>
+        <v>457670</v>
       </c>
       <c r="P2" t="n">
-        <v>369624</v>
+        <v>178773</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999867081642151</v>
+        <v>0.9999828338623047</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9723116159439087</v>
+        <v>0.9507448673248291</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9274773597717285</v>
+        <v>0.8928745985031128</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9122783541679382</v>
+        <v>0.8537448644638062</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7976776361465454</v>
+        <v>0.6826275587081909</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9461559653282166</v>
+        <v>0.8991304636001587</v>
       </c>
       <c r="W2" t="n">
-        <v>0.963958203792572</v>
+        <v>0.9305084347724915</v>
       </c>
       <c r="X2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>9714356</v>
+        <v>4854570</v>
       </c>
       <c r="AG2" t="n">
-        <v>5956664</v>
+        <v>2980268</v>
       </c>
       <c r="AH2" t="n">
-        <v>1601221</v>
+        <v>800821</v>
       </c>
       <c r="AI2" t="n">
-        <v>118175</v>
+        <v>59096</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917973</v>
+        <v>459081</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567423462867737</v>
+        <v>0.9567334651947021</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911146342754364</v>
+        <v>0.9111363887786865</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582749962806702</v>
+        <v>0.8581864833831787</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627725958824158</v>
+        <v>0.6625929474830627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020447134971619</v>
+        <v>0.9019822478294373</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -795,127 +795,127 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>9814984</v>
+        <v>4821812</v>
       </c>
       <c r="E3" t="n">
-        <v>320859</v>
+        <v>240204</v>
       </c>
       <c r="F3" t="n">
-        <v>6816</v>
+        <v>6554</v>
       </c>
       <c r="G3" t="n">
-        <v>610</v>
+        <v>591</v>
       </c>
       <c r="H3" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I3" t="n">
         <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>20139071</v>
+        <v>10069511</v>
       </c>
       <c r="K3" t="n">
-        <v>22409084</v>
+        <v>11096890</v>
       </c>
       <c r="L3" t="n">
-        <v>25801374</v>
+        <v>12785650</v>
       </c>
       <c r="M3" t="n">
-        <v>30804984</v>
+        <v>15348739</v>
       </c>
       <c r="N3" t="n">
-        <v>32626783</v>
+        <v>16306042</v>
       </c>
       <c r="O3" t="n">
-        <v>31759025</v>
+        <v>15855463</v>
       </c>
       <c r="P3" t="n">
-        <v>32431635</v>
+        <v>16209367</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9676211476325989</v>
+        <v>0.951177716255188</v>
       </c>
       <c r="S3" t="n">
-        <v>0.947228729724884</v>
+        <v>0.9047502279281616</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8921486139297485</v>
+        <v>0.8349337577819824</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5912784337997437</v>
+        <v>0.4986052811145782</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9460017085075378</v>
+        <v>0.8988143801689148</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9562250375747681</v>
+        <v>0.9249334931373596</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9714356</v>
+        <v>4854570</v>
       </c>
       <c r="Z3" t="n">
-        <v>398208</v>
+        <v>199283</v>
       </c>
       <c r="AA3" t="n">
-        <v>17110</v>
+        <v>8572</v>
       </c>
       <c r="AB3" t="n">
-        <v>13592</v>
+        <v>6807</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20139240</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>22249364</v>
+        <v>11127154</v>
       </c>
       <c r="AG3" t="n">
-        <v>25705317</v>
+        <v>12850470</v>
       </c>
       <c r="AH3" t="n">
-        <v>30700729</v>
+        <v>15349956</v>
       </c>
       <c r="AI3" t="n">
-        <v>32593417</v>
+        <v>16296642</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31714153</v>
+        <v>15856919</v>
       </c>
       <c r="AK3" t="n">
-        <v>32418947</v>
+        <v>16209464</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9577006697654724</v>
+        <v>0.957639753818512</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099981188774109</v>
+        <v>0.9100435376167297</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85770583152771</v>
+        <v>0.8576763868331909</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6622154712677002</v>
+        <v>0.6620287895202637</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015981554985046</v>
+        <v>0.9015854597091675</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -929,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>263379</v>
+        <v>234206</v>
       </c>
       <c r="E4" t="n">
-        <v>6200368</v>
+        <v>2962933</v>
       </c>
       <c r="F4" t="n">
-        <v>79570</v>
+        <v>75252</v>
       </c>
       <c r="G4" t="n">
-        <v>1301</v>
+        <v>1292</v>
       </c>
       <c r="H4" t="n">
         <v>1121</v>
@@ -947,109 +947,109 @@
         <v>59</v>
       </c>
       <c r="J4" t="n">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="K4" t="n">
-        <v>279500</v>
+        <v>249803</v>
       </c>
       <c r="L4" t="n">
-        <v>484828</v>
+        <v>355487</v>
       </c>
       <c r="M4" t="n">
-        <v>160151</v>
+        <v>133551</v>
       </c>
       <c r="N4" t="n">
-        <v>26763</v>
+        <v>20693</v>
       </c>
       <c r="O4" t="n">
-        <v>54813</v>
+        <v>51344</v>
       </c>
       <c r="P4" t="n">
-        <v>13820</v>
+        <v>13351</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999933838844299</v>
+        <v>0.9999914169311523</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9699606895446777</v>
+        <v>0.9509612321853638</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9372490048408508</v>
+        <v>0.898773193359375</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9021012783050537</v>
+        <v>0.8442345261573792</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6791425347328186</v>
+        <v>0.5762822031974792</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9460788369178772</v>
+        <v>0.8989723920822144</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9600760936737061</v>
+        <v>0.9277125597000122</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>410116</v>
+        <v>204986</v>
       </c>
       <c r="Z4" t="n">
-        <v>5956664</v>
+        <v>2980268</v>
       </c>
       <c r="AA4" t="n">
-        <v>165604</v>
+        <v>82895</v>
       </c>
       <c r="AB4" t="n">
-        <v>10994</v>
+        <v>5498</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>439220</v>
+        <v>219539</v>
       </c>
       <c r="AG4" t="n">
-        <v>580885</v>
+        <v>290667</v>
       </c>
       <c r="AH4" t="n">
-        <v>264406</v>
+        <v>132334</v>
       </c>
       <c r="AI4" t="n">
-        <v>60129</v>
+        <v>30093</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99685</v>
+        <v>49888</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572212696075439</v>
+        <v>0.9571864008903503</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9105718731880188</v>
+        <v>0.9105896949768066</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579903244972229</v>
+        <v>0.8579313158988953</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.662493884563446</v>
+        <v>0.662310779094696</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018213748931885</v>
+        <v>0.90178382396698</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
@@ -1059,19 +1059,19 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>9815</v>
+        <v>9344</v>
       </c>
       <c r="E5" t="n">
-        <v>149484</v>
+        <v>105741</v>
       </c>
       <c r="F5" t="n">
-        <v>1665521</v>
+        <v>779586</v>
       </c>
       <c r="G5" t="n">
-        <v>12639</v>
+        <v>9637</v>
       </c>
       <c r="H5" t="n">
-        <v>28779</v>
+        <v>28775</v>
       </c>
       <c r="I5" t="n">
         <v>626</v>
@@ -1080,106 +1080,106 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>328432</v>
+        <v>247495</v>
       </c>
       <c r="L5" t="n">
-        <v>345430</v>
+        <v>311930</v>
       </c>
       <c r="M5" t="n">
-        <v>201344</v>
+        <v>154124</v>
       </c>
       <c r="N5" t="n">
-        <v>72938</v>
+        <v>44757</v>
       </c>
       <c r="O5" t="n">
-        <v>54979</v>
+        <v>51523</v>
       </c>
       <c r="P5" t="n">
-        <v>16921</v>
+        <v>14509</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999948740005493</v>
+        <v>0.9999933838844299</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9814835786819458</v>
+        <v>0.9697065353393555</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9747119545936584</v>
+        <v>0.9593434929847717</v>
       </c>
       <c r="T5" t="n">
-        <v>0.988989531993866</v>
+        <v>0.9824759364128113</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9969633221626282</v>
+        <v>0.9960130453109741</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9966559410095215</v>
+        <v>0.9937337636947632</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9990636706352234</v>
+        <v>0.9983028769493103</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>16069</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>170194</v>
+        <v>85136</v>
       </c>
       <c r="AA5" t="n">
-        <v>1601221</v>
+        <v>800821</v>
       </c>
       <c r="AB5" t="n">
-        <v>19877</v>
+        <v>9950</v>
       </c>
       <c r="AC5" t="n">
-        <v>58238</v>
+        <v>29139</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>429060</v>
+        <v>214737</v>
       </c>
       <c r="AG5" t="n">
-        <v>589134</v>
+        <v>294595</v>
       </c>
       <c r="AH5" t="n">
-        <v>265644</v>
+        <v>132889</v>
       </c>
       <c r="AI5" t="n">
-        <v>60279</v>
+        <v>30169</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100189</v>
+        <v>50112</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735538363456726</v>
+        <v>0.9735455513000488</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643634557723999</v>
+        <v>0.9643480777740479</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983855664730072</v>
+        <v>0.9838436245918274</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.996332585811615</v>
+        <v>0.9963290691375732</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939122200012207</v>
+        <v>0.9939084053039551</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983846545219421</v>
+        <v>0.9983840584754944</v>
       </c>
     </row>
     <row r="6">
@@ -1189,22 +1189,22 @@
         <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>6272</v>
+        <v>6219</v>
       </c>
       <c r="E6" t="n">
-        <v>13561</v>
+        <v>8619</v>
       </c>
       <c r="F6" t="n">
-        <v>43861</v>
+        <v>21863</v>
       </c>
       <c r="G6" t="n">
-        <v>105516</v>
+        <v>44508</v>
       </c>
       <c r="H6" t="n">
-        <v>8751</v>
+        <v>7583</v>
       </c>
       <c r="I6" t="n">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12924</v>
+        <v>6466</v>
       </c>
       <c r="Z6" t="n">
-        <v>10697</v>
+        <v>5355</v>
       </c>
       <c r="AA6" t="n">
-        <v>21742</v>
+        <v>10880</v>
       </c>
       <c r="AB6" t="n">
-        <v>118175</v>
+        <v>59096</v>
       </c>
       <c r="AC6" t="n">
-        <v>13954</v>
+        <v>6987</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F7" t="n">
-        <v>29560</v>
+        <v>29545</v>
       </c>
       <c r="G7" t="n">
-        <v>11902</v>
+        <v>8919</v>
       </c>
       <c r="H7" t="n">
-        <v>963183</v>
+        <v>457670</v>
       </c>
       <c r="I7" t="n">
-        <v>12636</v>
+        <v>12187</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1624</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>59290</v>
+        <v>29657</v>
       </c>
       <c r="AB7" t="n">
-        <v>15136</v>
+        <v>7573</v>
       </c>
       <c r="AC7" t="n">
-        <v>917973</v>
+        <v>459081</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
@@ -1343,16 +1343,16 @@
         <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="G8" t="n">
-        <v>311</v>
+        <v>254</v>
       </c>
       <c r="H8" t="n">
-        <v>16035</v>
+        <v>13739</v>
       </c>
       <c r="I8" t="n">
-        <v>369624</v>
+        <v>178773</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
